--- a/Result/profitability/3050.xlsx
+++ b/Result/profitability/3050.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02500000000000002</v>
+        <v>-2.081668171172169e-17</v>
       </c>
       <c r="N2" t="n">
-        <v>30.61625</v>
+        <v>30.28125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05375000000000002</v>
+        <v>0.007499999999999979</v>
       </c>
       <c r="N3" t="n">
-        <v>28.1025</v>
+        <v>28.68375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08750000000000002</v>
+        <v>-0.05125000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>25.77125</v>
+        <v>25.7625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.91</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3375</v>
+        <v>-0.2575</v>
       </c>
       <c r="N5" t="n">
-        <v>24.4175</v>
+        <v>24.48375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3225</v>
+        <v>-0.29875</v>
       </c>
       <c r="N6" t="n">
-        <v>23.29</v>
+        <v>22.865</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3625</v>
+        <v>-0.31875</v>
       </c>
       <c r="N7" t="n">
-        <v>21.62625</v>
+        <v>22.39875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.37625</v>
+        <v>-0.31875</v>
       </c>
       <c r="N8" t="n">
-        <v>20.885</v>
+        <v>21.46625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32</v>
+        <v>-0.3200000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>22.55375</v>
@@ -2026,7 +2026,7 @@
         <v>1.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02875000000000003</v>
+        <v>0.02875</v>
       </c>
       <c r="N13" t="n">
         <v>26.35875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>301</v>
+      </c>
+      <c r="D75" t="n">
+        <v>199</v>
+      </c>
+      <c r="E75" t="n">
+        <v>103</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>74</v>
+      </c>
+      <c r="J75" t="n">
+        <v>73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>60</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05249999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.8375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.649999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1580557443915702</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.461538461538462</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5300000000000011</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01580202742993442</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
